--- a/testcase/Commerce_Hub_AI_Test_cases.xlsx
+++ b/testcase/Commerce_Hub_AI_Test_cases.xlsx
@@ -28406,31 +28406,26 @@
       <c r="H50" t="str">
         <v>Product is saved successfully, appears in All Products list with entered details, and total product count increases by 1</v>
       </c>
-      <c r="I50" t="str" xml:space="preserve">
-        <v xml:space="preserve">locator.fill: Error: strict mode violation: getByLabel(/Price/i) resolved to 2 elements:
-    1) &lt;input value="" placeholder="$0.00" class="h-11 w-full rounded-xl border border-[#DCE5EC] px-3 text-sm text-[#22354F] outline-none focus:border-[#20B8B0]"/&gt; aka getByRole('textbox', { name: 'Price', exact: true })
-    2) &lt;input value="" placeholder="$0.00" class="h-11 w-full rounded-xl border border-[#DCE5EC] px-3 text-sm text-[#22354F] outline-none focus:border-[#20B8B0]"/&gt; aka getByRole('textbox', { name: 'Compare At Price' })
-Call log:
-_x001b_[2m  - waiting for getByLabel(/Price/i)_x001b_[22m
-</v>
+      <c r="I50" t="str">
+        <v>Product 'Trail Runner Cap' (SKU: SKU-9001) was saved successfully. Initial product count: 7, Final product count: 8. Product appears in All Products list with entered details.</v>
       </c>
       <c r="J50" t="str">
         <v>Critical</v>
       </c>
       <c r="K50" t="str">
-        <v>7/24/2026, 4:11:13 PM</v>
+        <v>7/24/2026, 5:46:52 PM</v>
       </c>
       <c r="L50" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="M50" t="str">
-        <v>7/24/2026, 4:11:08 PM</v>
+        <v>7/24/2026, 5:46:43 PM</v>
       </c>
       <c r="N50" t="str">
-        <v>7/24/2026, 4:11:13 PM</v>
+        <v>7/24/2026, 5:46:52 PM</v>
       </c>
       <c r="O50" t="str">
-        <v>4.69</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="51" xml:space="preserve">
